--- a/inst/stimuli_2025/singpause_metadata_2025.xlsx
+++ b/inst/stimuli_2025/singpause_metadata_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/songbird/inst/stimuli_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F038B9-9478-3B43-8FF6-AFE2B4982643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E04A23D-C3FD-B44C-B5B7-C10D61A6B1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20700" xr2:uid="{21E2D67B-F3CA-354B-9F7D-B7019AB56455}"/>
+    <workbookView xWindow="0" yWindow="3180" windowWidth="35840" windowHeight="18000" xr2:uid="{21E2D67B-F3CA-354B-9F7D-B7019AB56455}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="185">
   <si>
     <t>song_name</t>
   </si>
@@ -561,13 +561,43 @@
   </si>
   <si>
     <t>https://musicassessr.com/assets/singpause/img/donkey_cuckoo.png</t>
+  </si>
+  <si>
+    <t>01_Main.mid</t>
+  </si>
+  <si>
+    <t>02_Sur_le_pont.mid</t>
+  </si>
+  <si>
+    <t>03_Kuckuck.mid</t>
+  </si>
+  <si>
+    <t>04_Drahtesel.mid</t>
+  </si>
+  <si>
+    <t>05_Wolfe.mid</t>
+  </si>
+  <si>
+    <t>06_Haltestelle.mid</t>
+  </si>
+  <si>
+    <t>07_Obwisana.mid</t>
+  </si>
+  <si>
+    <t>08_Vem_kan.mid</t>
+  </si>
+  <si>
+    <t>09_Moorhexe.mid</t>
+  </si>
+  <si>
+    <t>10_Karolinka.mid</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -596,6 +626,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -618,10 +655,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -957,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2DE21C-602C-E24D-B4E4-D80E898DE46A}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.5" customWidth="1"/>
@@ -988,14 +1026,8 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>165</v>
@@ -1003,881 +1035,1007 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E5" s="2"/>
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E8" s="2"/>
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E12" s="2"/>
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E22" s="2"/>
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>168</v>
-      </c>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E30" s="2"/>
+      <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D33" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E35" s="2"/>
+      <c r="A35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" t="s">
-        <v>154</v>
-      </c>
-      <c r="D41" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>170</v>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D42" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D45" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" t="s">
-        <v>156</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>171</v>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="D48" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D50" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>94</v>
-      </c>
-      <c r="B53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>163</v>
+      </c>
+      <c r="C54" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="D57" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" t="s">
-        <v>130</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" t="s">
+        <v>123</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" t="s">
+        <v>38</v>
+      </c>
+      <c r="C62" t="s">
+        <v>108</v>
+      </c>
+      <c r="D62" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>6</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B66" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" t="s">
+        <v>127</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
+        <v>128</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" t="s">
+        <v>129</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" t="s">
+        <v>115</v>
+      </c>
+      <c r="D70" t="s">
+        <v>131</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" t="s">
         <v>58</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C71" t="s">
         <v>116</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D71" t="s">
         <v>132</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>173</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D34">
-    <sortCondition ref="A1:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:D45">
+    <sortCondition ref="A12:A45"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{11567739-F919-CD43-AD9B-9D9D11F00AF5}"/>
-    <hyperlink ref="E6" r:id="rId2" xr:uid="{70095058-A8E0-944B-854C-5B24CE27AD18}"/>
-    <hyperlink ref="E13" r:id="rId3" xr:uid="{3FB6B1B7-63E3-A643-900F-A9EBE2B1756C}"/>
-    <hyperlink ref="E23" r:id="rId4" xr:uid="{C4143997-8766-F448-8038-70D8A48DF62C}"/>
-    <hyperlink ref="E31" r:id="rId5" xr:uid="{2B1FB8BF-D09D-9F45-9FF8-78471263974A}"/>
-    <hyperlink ref="E43" r:id="rId6" xr:uid="{CF990F20-0DC7-4648-9C40-9C063EC6066E}"/>
-    <hyperlink ref="E3" r:id="rId7" xr:uid="{707E148C-824F-3E49-A9BB-FC66090F6FE9}"/>
-    <hyperlink ref="E4" r:id="rId8" xr:uid="{4CEE8F5C-E4E4-EC42-844F-9250F31E38B9}"/>
-    <hyperlink ref="E7" r:id="rId9" xr:uid="{2EFC467E-BBA0-B746-AFBA-F1975A856C25}"/>
-    <hyperlink ref="E9" r:id="rId10" xr:uid="{36D308F4-E16B-6E4D-BDF6-C017F54BCC8D}"/>
-    <hyperlink ref="E10" r:id="rId11" xr:uid="{EF748111-DFDE-FD48-9BA4-A3441CE30C53}"/>
-    <hyperlink ref="E11" r:id="rId12" xr:uid="{644C1709-1BA6-0C4F-AB5E-210B535187BA}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{D351FF0F-ACD3-5247-83B7-9F930BDD53EF}"/>
-    <hyperlink ref="E15:E21" r:id="rId14" display="https://musicassessr.com/assets/singpause/img/bicycle.png" xr:uid="{E8BABDA3-C6FC-7E4F-B705-3FFC2BC6AEA8}"/>
-    <hyperlink ref="E24:E29" r:id="rId15" display="https://musicassessr.com/assets/singpause/img/wolves.png" xr:uid="{B69C0C19-6A31-BF4D-901A-0D7F7DAC6B95}"/>
-    <hyperlink ref="E32:E34" r:id="rId16" display="https://musicassessr.com/assets/singpause/img/bus-stop.png" xr:uid="{288D1E3E-2B7A-E742-A5F8-76AF0463E289}"/>
-    <hyperlink ref="E36:E41" r:id="rId17" display="https://musicassessr.com/assets/singpause/img/sailing-boat.png" xr:uid="{B285424C-35DC-8545-86FE-BE418426ABCE}"/>
-    <hyperlink ref="E44:E46" r:id="rId18" display="https://musicassessr.com/assets/singpause/img/sailing-boat.png" xr:uid="{670E9CFB-DB79-C340-8C2A-F61D02446993}"/>
-    <hyperlink ref="E48:E53" r:id="rId19" display="https://musicassessr.com/assets/singpause/img/dancer.png" xr:uid="{630CBEBF-1374-5042-8EE5-F9E04DF96262}"/>
-    <hyperlink ref="E55:E60" r:id="rId20" display="https://musicassessr.com/assets/singpause/img/path.png" xr:uid="{0C9C3D40-7610-FA4B-9F2E-0F66DAED9145}"/>
+    <hyperlink ref="E13" r:id="rId1" xr:uid="{11567739-F919-CD43-AD9B-9D9D11F00AF5}"/>
+    <hyperlink ref="E17" r:id="rId2" xr:uid="{70095058-A8E0-944B-854C-5B24CE27AD18}"/>
+    <hyperlink ref="E24" r:id="rId3" xr:uid="{3FB6B1B7-63E3-A643-900F-A9EBE2B1756C}"/>
+    <hyperlink ref="E34" r:id="rId4" xr:uid="{C4143997-8766-F448-8038-70D8A48DF62C}"/>
+    <hyperlink ref="E42" r:id="rId5" xr:uid="{2B1FB8BF-D09D-9F45-9FF8-78471263974A}"/>
+    <hyperlink ref="E54" r:id="rId6" xr:uid="{CF990F20-0DC7-4648-9C40-9C063EC6066E}"/>
+    <hyperlink ref="E14" r:id="rId7" xr:uid="{707E148C-824F-3E49-A9BB-FC66090F6FE9}"/>
+    <hyperlink ref="E15" r:id="rId8" xr:uid="{4CEE8F5C-E4E4-EC42-844F-9250F31E38B9}"/>
+    <hyperlink ref="E18" r:id="rId9" xr:uid="{2EFC467E-BBA0-B746-AFBA-F1975A856C25}"/>
+    <hyperlink ref="E20" r:id="rId10" xr:uid="{36D308F4-E16B-6E4D-BDF6-C017F54BCC8D}"/>
+    <hyperlink ref="E21" r:id="rId11" xr:uid="{EF748111-DFDE-FD48-9BA4-A3441CE30C53}"/>
+    <hyperlink ref="E22" r:id="rId12" xr:uid="{644C1709-1BA6-0C4F-AB5E-210B535187BA}"/>
+    <hyperlink ref="E25" r:id="rId13" xr:uid="{D351FF0F-ACD3-5247-83B7-9F930BDD53EF}"/>
+    <hyperlink ref="E26:E32" r:id="rId14" display="https://musicassessr.com/assets/singpause/img/bicycle.png" xr:uid="{E8BABDA3-C6FC-7E4F-B705-3FFC2BC6AEA8}"/>
+    <hyperlink ref="E35:E40" r:id="rId15" display="https://musicassessr.com/assets/singpause/img/wolves.png" xr:uid="{B69C0C19-6A31-BF4D-901A-0D7F7DAC6B95}"/>
+    <hyperlink ref="E43:E45" r:id="rId16" display="https://musicassessr.com/assets/singpause/img/bus-stop.png" xr:uid="{288D1E3E-2B7A-E742-A5F8-76AF0463E289}"/>
+    <hyperlink ref="E47:E52" r:id="rId17" display="https://musicassessr.com/assets/singpause/img/sailing-boat.png" xr:uid="{B285424C-35DC-8545-86FE-BE418426ABCE}"/>
+    <hyperlink ref="E55:E57" r:id="rId18" display="https://musicassessr.com/assets/singpause/img/sailing-boat.png" xr:uid="{670E9CFB-DB79-C340-8C2A-F61D02446993}"/>
+    <hyperlink ref="E59:E64" r:id="rId19" display="https://musicassessr.com/assets/singpause/img/dancer.png" xr:uid="{630CBEBF-1374-5042-8EE5-F9E04DF96262}"/>
+    <hyperlink ref="E66:E71" r:id="rId20" display="https://musicassessr.com/assets/singpause/img/path.png" xr:uid="{0C9C3D40-7610-FA4B-9F2E-0F66DAED9145}"/>
+    <hyperlink ref="E2" r:id="rId21" xr:uid="{A78B56CB-33BC-8F4A-AB03-970C20FCC5F9}"/>
+    <hyperlink ref="E3" r:id="rId22" xr:uid="{EA1E6CB7-147B-4A45-AFAC-033E8F9A72B3}"/>
+    <hyperlink ref="E4" r:id="rId23" xr:uid="{3D2B7782-CA56-3043-8918-B3AABCB2EA42}"/>
+    <hyperlink ref="E5" r:id="rId24" xr:uid="{15161094-6670-2D4F-86C4-AAB62E813976}"/>
+    <hyperlink ref="E6" r:id="rId25" xr:uid="{1FCDC529-ECBA-7D4D-AC8A-C14A6E6EB214}"/>
+    <hyperlink ref="E7" r:id="rId26" xr:uid="{6B90BD8B-3D50-DA42-8929-0B4E4926BB90}"/>
+    <hyperlink ref="E8" r:id="rId27" display="https://musicassessr.com/assets/singpause/img/sailing-boat.png" xr:uid="{25B2A0F4-9895-4F4A-B68B-311457D11A42}"/>
+    <hyperlink ref="E9" r:id="rId28" xr:uid="{FEDB6CB1-1DE5-6B40-9AA1-76A26B4B7F70}"/>
+    <hyperlink ref="E10" r:id="rId29" display="https://musicassessr.com/assets/singpause/img/dancer.png" xr:uid="{73C9B723-B8D5-664C-B0A3-D83E84414FDB}"/>
+    <hyperlink ref="E11" r:id="rId30" display="https://musicassessr.com/assets/singpause/img/path.png" xr:uid="{9F46F157-A55C-404D-8C88-5CA9A42F16A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
